--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260612.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260612.xlsx
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>三陽工業</t>
+          <t>寶成</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>16,092,000</t>
+          <t>37,817,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>寶成</t>
+          <t>三陽工業</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>37,817,000</t>
+          <t>16,092,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
